--- a/Archivos_Compartidos/Conciliaciones Contabilidad/Diccionario_SIGMA_Consolidado_por_Esquema_V2.xlsx
+++ b/Archivos_Compartidos/Conciliaciones Contabilidad/Diccionario_SIGMA_Consolidado_por_Esquema_V2.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\SAMMX\Documents\GitHub\SAM_Santander\Archivos_Compartidos\Conciliaciones Contabilidad\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{00E5F908-0633-4E2C-A394-4DFA560089A6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{ECA3AABE-FC67-438C-80B8-D92609B4E541}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="448" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="448" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Índice" sheetId="1" r:id="rId1"/>
@@ -7060,6 +7060,12 @@
     </row>
   </sheetData>
   <mergeCells count="13">
+    <mergeCell ref="A153:G153"/>
+    <mergeCell ref="A168:G168"/>
+    <mergeCell ref="A194:G194"/>
+    <mergeCell ref="A93:G93"/>
+    <mergeCell ref="A115:G115"/>
+    <mergeCell ref="A130:G130"/>
     <mergeCell ref="B7:F7"/>
     <mergeCell ref="B28:F28"/>
     <mergeCell ref="A63:G63"/>
@@ -7067,12 +7073,6 @@
     <mergeCell ref="A5:G5"/>
     <mergeCell ref="A43:G43"/>
     <mergeCell ref="A26:G26"/>
-    <mergeCell ref="A153:G153"/>
-    <mergeCell ref="A168:G168"/>
-    <mergeCell ref="A194:G194"/>
-    <mergeCell ref="A93:G93"/>
-    <mergeCell ref="A115:G115"/>
-    <mergeCell ref="A130:G130"/>
   </mergeCells>
   <phoneticPr fontId="5" type="noConversion"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
